--- a/SGC-CKN/Excel/5d8f0481-aaf5-4102-a1f7-71154a9c7d1d_Lô_CT-02_PH-136_D800_26-03-2026.xlsx
+++ b/SGC-CKN/Excel/5d8f0481-aaf5-4102-a1f7-71154a9c7d1d_Lô_CT-02_PH-136_D800_26-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="76">
   <si>
     <t>Dự án</t>
   </si>
@@ -102,7 +102,7 @@
 26/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">01:57
+    <t xml:space="preserve">01:53
 26/03/2026</t>
   </si>
   <si>
@@ -115,17 +115,21 @@
     <t>Cát pha xám ghi, xám nâu TT dẻo</t>
   </si>
   <si>
-    <t xml:space="preserve">02:15
+    <t xml:space="preserve">01:54
 26/03/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">02:05
+26/03/2026</t>
+  </si>
+  <si>
     <t>9</t>
   </si>
   <si>
     <t>Sét xám trắng, xám xanh dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">02:16
+    <t xml:space="preserve">02:06
 26/03/2026</t>
   </si>
   <si>
@@ -399,12 +403,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFFECACA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFECACA"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -574,17 +578,17 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1232,19 +1236,19 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-3.31</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-7.3</v>
       </c>
       <c r="H11" s="5">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="I11" s="5">
         <v>7.3</v>
       </c>
       <c r="J11" s="8">
-        <v>6.47</v>
+        <v>13.27</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1261,10 +1265,10 @@
         <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12" s="9">
         <v>-7.3</v>
@@ -1273,13 +1277,13 @@
         <v>-9.4</v>
       </c>
       <c r="H12" s="9">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
       <c r="I12" s="9">
         <v>2.1</v>
       </c>
       <c r="J12" s="8">
-        <v>7</v>
+        <v>11.45</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1287,89 +1291,89 @@
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F13" s="12">
         <v>-9.4</v>
       </c>
       <c r="G13" s="12">
-        <v>-12.6</v>
+        <v>-17.6</v>
       </c>
       <c r="H13" s="12">
-        <v>0.73</v>
+        <v>0.9</v>
       </c>
       <c r="I13" s="12">
-        <v>3.2</v>
-      </c>
-      <c r="J13" s="15">
-        <v>4.36</v>
+        <v>8.2</v>
+      </c>
+      <c r="J13" s="8">
+        <v>9.11</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="16" t="s">
+      <c r="A14" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="18" t="s">
+      <c r="C14" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="D14" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="16">
-        <v>-12.6</v>
-      </c>
-      <c r="G14" s="16">
+      <c r="E14" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="15">
+        <v>-17.6</v>
+      </c>
+      <c r="G14" s="15">
         <v>-21.33</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="15">
         <v>0.98</v>
       </c>
-      <c r="I14" s="16">
-        <v>8.73</v>
-      </c>
-      <c r="J14" s="8">
-        <v>8.88</v>
-      </c>
-      <c r="K14" s="17" t="s">
+      <c r="I14" s="15">
+        <v>3.73</v>
+      </c>
+      <c r="J14" s="18">
+        <v>3.79</v>
+      </c>
+      <c r="K14" s="16" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F15" s="19">
         <v>-21.33</v>
@@ -1383,7 +1387,7 @@
       <c r="I15" s="19">
         <v>4.07</v>
       </c>
-      <c r="J15" s="15">
+      <c r="J15" s="18">
         <v>4.98</v>
       </c>
       <c r="K15" s="20" t="s">
@@ -1392,19 +1396,19 @@
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F16" s="22">
         <v>-25.4</v>
@@ -1427,19 +1431,19 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F17" s="25">
         <v>-35.26</v>
@@ -1453,7 +1457,7 @@
       <c r="I17" s="25">
         <v>2.62</v>
       </c>
-      <c r="J17" s="15">
+      <c r="J17" s="18">
         <v>1.99</v>
       </c>
       <c r="K17" s="26" t="s">
@@ -1462,19 +1466,19 @@
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F18" s="28">
         <v>-37.88</v>
@@ -1488,7 +1492,7 @@
       <c r="I18" s="28">
         <v>1.62</v>
       </c>
-      <c r="J18" s="15">
+      <c r="J18" s="18">
         <v>1.23</v>
       </c>
       <c r="K18" s="29" t="s">
@@ -1497,19 +1501,19 @@
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F19" s="31">
         <v>-39.5</v>
@@ -1532,19 +1536,19 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F20" s="34">
         <v>-43.43</v>
@@ -1558,7 +1562,7 @@
       <c r="I20" s="34">
         <v>1.35</v>
       </c>
-      <c r="J20" s="15">
+      <c r="J20" s="18">
         <v>4.26</v>
       </c>
       <c r="K20" s="35" t="s">
@@ -1567,7 +1571,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -1673,31 +1677,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1714,19 +1718,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-3.31</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-7.3</v>
       </c>
       <c r="G2" s="5">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="H2" s="5">
         <v>7.3</v>
       </c>
       <c r="I2" s="8">
-        <v>11.84</v>
+        <v>13.27</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1749,13 +1753,13 @@
         <v>-9.4</v>
       </c>
       <c r="G3" s="9">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
       <c r="H3" s="9">
         <v>2.1</v>
       </c>
       <c r="I3" s="8">
-        <v>7</v>
+        <v>11.45</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1766,7 +1770,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="12">
         <v>1</v>
@@ -1775,45 +1779,45 @@
         <v>-9.4</v>
       </c>
       <c r="F4" s="12">
-        <v>-12.6</v>
+        <v>-17.6</v>
       </c>
       <c r="G4" s="12">
-        <v>0.73</v>
+        <v>0.9</v>
       </c>
       <c r="H4" s="12">
-        <v>3.2</v>
-      </c>
-      <c r="I4" s="15">
-        <v>4.36</v>
+        <v>8.2</v>
+      </c>
+      <c r="I4" s="8">
+        <v>9.11</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
+      <c r="A5" s="15">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="16">
+      <c r="C5" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="15">
         <v>1</v>
       </c>
-      <c r="E5" s="16">
-        <v>-12.6</v>
-      </c>
-      <c r="F5" s="16">
+      <c r="E5" s="15">
+        <v>-17.6</v>
+      </c>
+      <c r="F5" s="15">
         <v>-21.33</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="15">
         <v>0.98</v>
       </c>
-      <c r="H5" s="16">
-        <v>8.73</v>
-      </c>
-      <c r="I5" s="8">
-        <v>8.88</v>
+      <c r="H5" s="15">
+        <v>3.73</v>
+      </c>
+      <c r="I5" s="18">
+        <v>3.79</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1824,7 +1828,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1841,7 +1845,7 @@
       <c r="H6" s="19">
         <v>4.07</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="18">
         <v>4.98</v>
       </c>
     </row>
@@ -1853,7 +1857,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1882,7 +1886,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1899,7 +1903,7 @@
       <c r="H8" s="25">
         <v>2.62</v>
       </c>
-      <c r="I8" s="15">
+      <c r="I8" s="18">
         <v>1.99</v>
       </c>
     </row>
@@ -1911,7 +1915,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1928,7 +1932,7 @@
       <c r="H9" s="28">
         <v>1.62</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I9" s="18">
         <v>1.23</v>
       </c>
     </row>
@@ -1940,7 +1944,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1969,7 +1973,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
@@ -1986,13 +1990,13 @@
       <c r="H11" s="34">
         <v>1.35</v>
       </c>
-      <c r="I11" s="15">
+      <c r="I11" s="18">
         <v>4.26</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B12" s="39" t="s">
         <v>30</v>
@@ -2004,19 +2008,19 @@
         <v>10</v>
       </c>
       <c r="E12" s="39">
-        <v>-3.31</v>
+        <v>0</v>
       </c>
       <c r="F12" s="39">
         <v>-44.78</v>
       </c>
       <c r="G12" s="39">
-        <v>8.2</v>
+        <v>8.18</v>
       </c>
       <c r="H12" s="39">
         <v>44.78</v>
       </c>
       <c r="I12" s="39">
-        <v>5.46</v>
+        <v>5.47</v>
       </c>
     </row>
   </sheetData>
